--- a/stories/arbres/ATOM-SOC.CUI.001-04.xlsx
+++ b/stories/arbres/ATOM-SOC.CUI.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>C'est le soir. Olivier entre dans la cuisine. Papa est là. Olivier dit : je veux aider. Papa sourit. Papa dit : tu fais une tâche sûre, avec un adulte. Olivier ouvre l'eau. Il lave une tomate. L'eau est froide. La tomate est lisse. Olivier pose la tomate. Ensuite, il prend une cuillère. Il pose la cuillère près de l'assiette. Puis Olivier va au pain. Il apporte le pain à table. Papa dit : merci. Laver. Poser. Apporter. Ce sont des tâches sûres. Plus tard, maman arrive. Olivier se souvient. Il lave une feuille de salade. C'est encore une tâche sûre, avec un adulte. Maman dit : tu as transféré le geste. Olivier reste avec papa. Ils préparent ensemble.</t>
+          <t>C'est le soir. Olivier entre dans la cuisine. Papa est là. Je veux aider. Papa sourit. Tu fais une tâche sûre, avec un adulte. Olivier ouvre l'eau. Il lave une tomate. L'eau est froide. La tomate est lisse. Olivier pose la tomate. Ensuite, il prend une cuillère. Il pose la cuillère près de l'assiette. Puis Olivier va au pain. Il apporte le pain à table. Merci. Laver. Poser. Apporter. Ce sont des tâches sûres. Plus tard, maman arrive. Olivier se souvient. Il lave une feuille de salade. C'est encore une tâche sûre, avec un adulte. Tu as transféré le geste. Olivier reste avec papa. Ils préparent ensemble.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,18 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Olivier entre dans la cuisine. Papa est là.
+enfant-m|Je veux aider. Papa sourit.
+papa|Tu fais une tâche sûre, avec un adulte.
+narrateur|Olivier ouvre l'eau. Il lave une tomate. L'eau est froide. La tomate est lisse. Olivier pose la tomate. Ensuite, il prend une cuillère. Il pose la cuillère près de l'assiette. Puis Olivier va au pain. Il apporte le pain à table.
+papa|Merci. Laver. Poser. Apporter. Ce sont des tâches sûres. Plus tard, maman arrive.
+narrateur|Olivier se souvient. Il lave une feuille de salade. C'est encore une tâche sûre, avec un adulte.
+maman|Tu as transféré le geste.
+narrateur|Olivier reste avec papa. Ils préparent ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1493,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Olivier aide papa. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1666,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Olivier a lavé la tomate. Il a posé la cuillère. Il a apporté le pain. Avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1829,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Olivier s'assoit. Il croque un morceau de pain. Papa est près de lui.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1996,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2036,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.CUI.001-04.xlsx
+++ b/stories/arbres/ATOM-SOC.CUI.001-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1317,6 +1322,7 @@
 narrateur|Olivier reste avec papa. Ils préparent ensemble.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1500,6 +1506,7 @@
           <t>narrateur|Olivier aide papa. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1671,6 +1678,7 @@
           <t>narrateur|Olivier a lavé la tomate. Il a posé la cuillère. Il a apporté le pain. Avec un adulte.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1834,6 +1842,7 @@
           <t>narrateur|Olivier s'assoit. Il croque un morceau de pain. Papa est près de lui.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2001,6 +2010,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2019,7 +2029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2043,6 +2053,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2244,6 +2268,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SOC.CUI.001-04.xlsx
+++ b/stories/arbres/ATOM-SOC.CUI.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Olivier aide papa à préparer</t>
+          <t>La crêpe dorée d'Aniss</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Aniss veut une crêpe dorée. La première reste trop pâle. Ils attendent. La deuxième dore. Ils la plient, tiède, près de la fenêtre.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>C'est le soir. Olivier entre dans la cuisine. Papa est là. Je veux aider. Papa sourit. Tu fais une tâche sûre, avec un adulte. Olivier ouvre l'eau. Il lave une tomate. L'eau est froide. La tomate est lisse. Olivier pose la tomate. Ensuite, il prend une cuillère. Il pose la cuillère près de l'assiette. Puis Olivier va au pain. Il apporte le pain à table. Merci. Laver. Poser. Apporter. Ce sont des tâches sûres. Plus tard, maman arrive. Olivier se souvient. Il lave une feuille de salade. C'est encore une tâche sûre, avec un adulte. Tu as transféré le geste. Olivier reste avec papa. Ils préparent ensemble.</t>
+          <t>Un nuage blanc sort de la poêle. Ça sent le beurre qui fond. La fenêtre laisse entrer un carré clair. Un torchon pend près du bois. Tu as vu le nuage, Aniss ? Il monte. Oui. La poêle est chaude. En ce moment, Aniss veut une crêpe dorée. Je veux celle qui brille. On la fait ensemble ? Oui. Je peux aider ? Oui, avec nous. Aniss tient le bol des deux mains. La pâte est lisse, un peu épaisse. Papa verse un rond dans la poêle. Ça fait un petit chuintement. Elle est blanche. On attend ? Oui. Ils regardent le rond pâle. Les bords restent trop clairs. Papa la retourne. L'autre côté est pâle aussi. Elle n'est pas dorée. La première est souvent comme ça. On en fait une autre ? Oui. Aniss verse un peu de pâte. Maman guide sa main. Le second rond s'étale, plus mince. On laisse le temps. Un bord devient brun tout doux. Ça sent plus fort le beurre. Elle dore ! Tu vois la couleur ? Oui, comme le soleil. Papa la tourne. Le dessous est tacheté, tout beau. Merci, Aniss. Tu as versé avec moi. Ils plient la crêpe en deux. Puis encore, en petit triangle. Aniss l'apporte à table. Elle est tiède. On s'assoit près du carreau ? Oui. Maman pose un peu de sucre. Aniss croque le coin. Ça craque, puis c'est mou. C'est doré. La deuxième a réussi. La première, trop pâle, attend. Papa la plie aussi, pour lui. La mienne brille. Oui. Un peu de vapeur sort encore. Le torchon a une tache de beurre. Tu as aidé pour la deuxième. On a attendu. Oui. Le carré clair glisse sur la table. Aniss lèche un grain de sucre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;C'est le soir. Olivier entre dans la cuisine. Papa est là. Olivier dit : je veux aider. Papa sourit. Papa dit : tu fais une &lt;emphasis level="moderate"&gt;tâche&lt;/emphasis&gt; sûre, avec un adulte. Olivier ouvre l'eau. Il lave une tomate. L'eau est froide. La tomate est lisse. Olivier pose la tomate. Ensuite, il prend une cuillère. Il pose la cuillère près de l'assiette. Puis Olivier va au pain. Il apporte le pain à table. Papa dit : merci. Laver. Poser. Apporter. Ce sont des tâches sûres. Plus tard, maman arrive. Olivier se souvient. Il lave une feuille de salade. C'est encore une tâche sûre, avec un adulte. Maman dit : tu as transféré le geste. Olivier reste avec papa. Ils préparent ensemble.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un nuage blanc sort de la poêle. Ça sent le beurre qui fond. La fenêtre laisse entrer un carré clair. Un torchon pend près du bois. Tu as vu le nuage, Aniss ? Il monte. Oui. La poêle est chaude. En ce moment, Aniss veut une crêpe dorée. Je veux celle qui brille. On la fait ensemble ? Oui. Je peux aider ? Oui, avec nous. Aniss tient le bol des deux mains. La pâte est lisse, un peu épaisse. Papa verse un rond dans la poêle. Ça fait un petit chuintement. Elle est blanche. On attend ? Oui. Ils regardent le rond pâle. Les bords restent trop clairs. Papa la retourne. L'autre côté est pâle aussi. Elle n'est pas dorée. La première est souvent comme ça. On en fait une autre ? Oui. Aniss verse un peu de pâte. Maman guide sa main. Le second rond s'étale, plus mince. On laisse le temps. Un bord devient brun tout doux. Ça sent plus fort le beurre. Elle dore ! Tu vois la couleur ? Oui, comme le soleil. Papa la tourne. Le dessous est tacheté, tout beau. Merci, Aniss. Tu as versé avec moi. Ils plient la crêpe en deux. Puis encore, en petit triangle. Aniss l'apporte à table. Elle est tiède. On s'assoit près du carreau ? Oui. Maman pose un peu de sucre. Aniss croque le coin. Ça craque, puis c'est mou. C'est doré. La deuxième a réussi. La première, trop pâle, attend. Papa la plie aussi, pour lui. La mienne brille. Oui. Un peu de vapeur sort encore. Le torchon a une tache de beurre. Tu as aidé pour la deuxième. On a attendu. Oui. Le carré clair glisse sur la table. Aniss lèche un grain de sucre.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,17 +1324,72 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|C'est le soir. Olivier entre dans la cuisine. Papa est là.
-enfant-m|Je veux aider. Papa sourit.
-papa|Tu fais une tâche sûre, avec un adulte.
-narrateur|Olivier ouvre l'eau. Il lave une tomate. L'eau est froide. La tomate est lisse. Olivier pose la tomate. Ensuite, il prend une cuillère. Il pose la cuillère près de l'assiette. Puis Olivier va au pain. Il apporte le pain à table.
-papa|Merci. Laver. Poser. Apporter. Ce sont des tâches sûres. Plus tard, maman arrive.
-narrateur|Olivier se souvient. Il lave une feuille de salade. C'est encore une tâche sûre, avec un adulte.
-maman|Tu as transféré le geste.
-narrateur|Olivier reste avec papa. Ils préparent ensemble.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Un nuage blanc sort de la poêle.
+narrateur|Ça sent le beurre qui fond.
+narrateur|La fenêtre laisse entrer un carré clair.
+narrateur|Un torchon pend près du bois.
+papa|Tu as vu le nuage, Aniss ?
+enfant-m|Il monte.
+papa|Oui.
+papa|La poêle est chaude.
+narrateur|En ce moment, Aniss veut une crêpe dorée.
+enfant-m|Je veux celle qui brille.
+maman|On la fait ensemble ?
+enfant-m|Oui.
+enfant-m|Je peux aider ?
+maman|Oui, avec nous.
+narrateur|Aniss tient le bol des deux mains.
+narrateur|La pâte est lisse, un peu épaisse.
+narrateur|Papa verse un rond dans la poêle.
+narrateur|Ça fait un petit chuintement.
+enfant-m|Elle est blanche.
+papa|On attend ?
+enfant-m|Oui.
+narrateur|Ils regardent le rond pâle.
+narrateur|Les bords restent trop clairs.
+narrateur|Papa la retourne.
+narrateur|L'autre côté est pâle aussi.
+enfant-m|Elle n'est pas dorée.
+maman|La première est souvent comme ça.
+maman|On en fait une autre ?
+enfant-m|Oui.
+narrateur|Aniss verse un peu de pâte.
+narrateur|Maman guide sa main.
+narrateur|Le second rond s'étale, plus mince.
+papa|On laisse le temps.
+narrateur|Un bord devient brun tout doux.
+narrateur|Ça sent plus fort le beurre.
+enfant-m|Elle dore !
+maman|Tu vois la couleur ?
+enfant-m|Oui, comme le soleil.
+narrateur|Papa la tourne.
+narrateur|Le dessous est tacheté, tout beau.
+maman|Merci, Aniss.
+maman|Tu as versé avec moi.
+narrateur|Ils plient la crêpe en deux.
+narrateur|Puis encore, en petit triangle.
+narrateur|Aniss l'apporte à table.
+enfant-m|Elle est tiède.
+papa|On s'assoit près du carreau ?
+enfant-m|Oui.
+narrateur|Maman pose un peu de sucre.
+narrateur|Aniss croque le coin.
+narrateur|Ça craque, puis c'est mou.
+enfant-m|C'est doré.
+papa|La deuxième a réussi.
+narrateur|La première, trop pâle, attend.
+narrateur|Papa la plie aussi, pour lui.
+enfant-m|La mienne brille.
+maman|Oui.
+narrateur|Un peu de vapeur sort encore.
+narrateur|Le torchon a une tache de beurre.
+papa|Tu as aidé pour la deuxième.
+enfant-m|On a attendu.
+papa|Oui.
+narrateur|Le carré clair glisse sur la table.
+narrateur|Aniss lèche un grain de sucre.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1347,27 +1414,27 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>Aniss aide pour les crêpes. Que fait-il ?</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Aniss aide pour les crêpes. Que fait-il ?</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
           <t>Olivier aide papa. Que fait-il ?</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Olivier aide papa. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Olivier aide papa. Que fait-il ?</t>
-        </is>
-      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>aider</t>
+          <t>verser</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>aider | laver | apporter | avec papa</t>
+          <t>verser | aider | la crêpe | avec papa | avec maman | il verse | attendre</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1382,7 +1449,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il lave la tomate. Que fait Olivier ?</t>
+          <t>Aniss aide pour les crêpes. Que fait-il ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1424,14 +1491,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1503,10 +1570,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Olivier aide papa. Que fait-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Aniss aide pour les crêpes.
+narrateur|Que fait-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1531,12 +1598,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Olivier a lavé la tomate. Il a posé la cuillère. Il a apporté le pain. Avec un adulte.</t>
+          <t>La première crêpe était trop pâle. Aniss a versé la deuxième. Elle a doré. Tu as aidé, Aniss. On a attendu. Oui. Le triangle tiède est dans l'assiette. Ça sent encore le beurre.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Olivier a lavé la tomate. Il a posé la cuillère. Il a apporté le pain. &lt;emphasis level="moderate"&gt;avec&lt;/emphasis&gt; un adulte.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>La première crêpe était trop pâle. Aniss a versé la deuxième. Elle a doré. Tu as aidé, Aniss. On a attendu. Oui. Le triangle tiède est dans l'assiette. Ça sent encore le beurre.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1599,7 +1666,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1675,10 +1742,16 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Olivier a lavé la tomate. Il a posé la cuillère. Il a apporté le pain. Avec un adulte.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|La première crêpe était trop pâle.
+narrateur|Aniss a versé la deuxième.
+narrateur|Elle a doré.
+maman|Tu as aidé, Aniss.
+enfant-m|On a attendu.
+papa|Oui.
+narrateur|Le triangle tiède est dans l'assiette.
+narrateur|Ça sent encore le beurre.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1703,12 +1776,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Olivier s'assoit. Il croque un morceau de pain. Papa est près de lui.</t>
+          <t>Aniss plie le dernier coin. Il reste du sucre ? Sur mes doigts. Merci pour la pâte. La mienne était dorée. Oui. La poêle se tait. Le nuage blanc n'est plus là. Le torchon sent le beurre.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Olivier s'assoit. Il croque un morceau de pain. Papa est près de lui.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss plie le dernier coin. Il reste du sucre ? Sur mes doigts. Merci pour la pâte. La mienne était dorée. Oui. La poêle se tait. Le nuage blanc n'est plus là. Le torchon sent le beurre.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1771,7 +1844,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1839,10 +1912,17 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Olivier s'assoit. Il croque un morceau de pain. Papa est près de lui.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Aniss plie le dernier coin.
+papa|Il reste du sucre ?
+enfant-m|Sur mes doigts.
+maman|Merci pour la pâte.
+enfant-m|La mienne était dorée.
+papa|Oui.
+narrateur|La poêle se tait.
+narrateur|Le nuage blanc n'est plus là.
+narrateur|Le torchon sent le beurre.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1867,12 +1947,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss regarde le carré de lumière. Elle était comme le soleil. Oui. Un grain de sucre brille encore. La crêpe tiède sent le beurre.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss regarde le carré de lumière. Elle était comme le soleil. Oui. Un grain de sucre brille encore. La crêpe tiède sent le beurre.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1935,7 +2015,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2007,10 +2087,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Aniss regarde le carré de lumière.
+enfant-m|Elle était comme le soleil.
+maman|Oui.
+narrateur|Un grain de sucre brille encore.
+narrateur|La crêpe tiède sent le beurre.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2029,7 +2112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2067,6 +2150,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.CUI.001-04.xlsx
+++ b/stories/arbres/ATOM-SOC.CUI.001-04.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cuisine</t>
+          <t>cuisine le dimanche, poêle et vapeur</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Olivier, papa, maman</t>
+          <t>Aniss, papa, maman</t>
         </is>
       </c>
     </row>
